--- a/consent_forms/031_editable_chemical_peel_consent--consent_forms.xlsx
+++ b/consent_forms/031_editable_chemical_peel_consent--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -930,17 +930,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>consent_type_choices</t>
+          <t>chemical_peel_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>microdermabrasion</t>
+          <t>light_peel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Microdermabrasion</t>
+          <t>Light Peel</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>light_peel</t>
+          <t>medium_peel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Light Peel</t>
+          <t>Medium Peel</t>
         </is>
       </c>
     </row>
@@ -969,29 +969,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>medium_peel</t>
+          <t>deep_peel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medium Peel</t>
+          <t>Deep Peel</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>chemical_peel_type_choices</t>
+          <t>chemical_peel_concentration_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>deep_peel</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Deep Peel</t>
+          <t>5%</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>15%</t>
         </is>
       </c>
     </row>
@@ -1037,29 +1037,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>chemical_peel_concentration_choices</t>
+          <t>num_passes_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1088,29 +1088,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>num_passes_choices</t>
+          <t>num_passes_duration_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1139,29 +1139,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>num_passes_duration_choices</t>
+          <t>num_passes_interval_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1190,29 +1190,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>num_passes_interval_choices</t>
+          <t>chemical_peel_solution_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>glycolic_acid</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Glycolic Acid</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>glycolic_acid</t>
+          <t>salicylic_acid</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Glycolic Acid</t>
+          <t>Salicylic Acid</t>
         </is>
       </c>
     </row>
@@ -1241,29 +1241,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>salicylic_acid</t>
+          <t>lactic_acid</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salicylic Acid</t>
+          <t>Lactic Acid</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chemical_peel_solution_choices</t>
+          <t>num_passes_interval_unit_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lactic_acid</t>
+          <t>minutes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lactic Acid</t>
+          <t>minutes</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>minutes</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>minutes</t>
+          <t>hours</t>
         </is>
       </c>
     </row>
@@ -1292,29 +1292,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hours</t>
+          <t>days</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hours</t>
+          <t>days</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>num_passes_interval_unit_choices</t>
+          <t>chemical_peel_product_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>product_a</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>Product A</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>product_a</t>
+          <t>product_b</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Product A</t>
+          <t>Product B</t>
         </is>
       </c>
     </row>
@@ -1343,29 +1343,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>product_b</t>
+          <t>product_c</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Product B</t>
+          <t>Product C</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chemical_peel_product_choices</t>
+          <t>treatment_area_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>product_c</t>
+          <t>face</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Product C</t>
+          <t>Face</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>face</t>
+          <t>neck</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Face</t>
+          <t>Neck</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>neck</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Neck</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>chest</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Chest</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>chest</t>
+          <t>hands</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chest</t>
+          <t>Hands</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>hands</t>
+          <t>fingers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hands</t>
+          <t>Fingers</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>fingers</t>
+          <t>toes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fingers</t>
+          <t>Toes</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>toes</t>
+          <t>feet</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Toes</t>
+          <t>Feet</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>feet</t>
+          <t>ears</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Feet</t>
+          <t>Ears</t>
         </is>
       </c>
     </row>
@@ -1513,29 +1513,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ears</t>
+          <t>eyelids</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ears</t>
+          <t>Eyelids</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>treatment_area_choices</t>
+          <t>num_passes_interval_unit_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eyelids</t>
+          <t>minutes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eyelids</t>
+          <t>minutes</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>minutes</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>minutes</t>
+          <t>hours</t>
         </is>
       </c>
     </row>
@@ -1564,29 +1564,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>hours</t>
+          <t>days</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>hours</t>
+          <t>days</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>num_passes_interval_unit_choices</t>
+          <t>num_passes_interval_duration_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>minutes</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>minutes</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>minutes</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>minutes</t>
+          <t>hours</t>
         </is>
       </c>
     </row>
@@ -1615,27 +1615,10 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>hours</t>
+          <t>days</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
-        <is>
-          <t>hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>num_passes_interval_duration_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
         <is>
           <t>days</t>
         </is>
